--- a/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_03_20_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_01_Giới thiệu _ Foundation LLM/Day_01_Phan_03_20_Cau.xlsx
@@ -631,7 +631,7 @@
       </c>
       <c r="G3" s="3" t="n"/>
       <c r="H3" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="4" t="n">
         <v>60</v>
@@ -639,7 +639,7 @@
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: So sánh từng chỉ số key với chỉ số query.</t>
+          <t>Trong decoder nhân quả, query tại vị trí 3 chỉ được phép chú ý tới các key tại vị trí &lt;= 3. Việc mask cho phép key 4 làm rò rỉ thông tin tương lai vào bước suy luận hiện tại.</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="G6" s="3" t="n"/>
       <c r="H6" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>60</v>
@@ -783,7 +783,7 @@
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Residual nghĩa là giữ một đường đi tắt của biểu diễn trước tầng biến đổi.</t>
+          <t>Đường kết nối tắt residual (residual skip connection) quanh khối attention nhận đầu vào ban đầu `x` và cộng trực tiếp với đầu ra của tầng `Attention(x)`, tạo thành `x + Attention(x)` trước khi đi vào LayerNorm.</t>
         </is>
       </c>
     </row>
@@ -812,7 +812,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4</t>
+          <t>o2 → o4 → o1 → o3</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -840,7 +840,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Theo dõi biến nào phải được tạo trước khi xuất hiện ở vế phải.</t>
+          <t>Thứ tự qua khối Transformer (Post-Norm): attention tính a = Attention(x) (o2) -&gt; residual &amp; norm tính r1 = Norm(x + a) (o4) -&gt; feed-forward tính f = FFN(r1) (o1) -&gt; residual &amp; norm thứ hai tính r2 = Norm(r1 + f) (o3).</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-C, 2-B, 3-A</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -896,7 +896,7 @@
       <c r="J8" s="3" t="n"/>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tách chuỗi nguồn khỏi tiền tố token đích, rồi hỏi đường nào nối hai phía.</t>
+          <t>Self-attention của encoder (x1) truy cập các vị trí nguồn trong đầu vào encoder (r1); Causal self-attention của decoder (x2) truy cập các vị trí token đích hiện tại hoặc quá khứ (r2); Cross-attention của decoder (x3) truy cập đầu ra encoder khi decoder sinh token đích (r3).</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>60</v>
@@ -942,7 +942,7 @@
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Kiểm tra có hai ngăn xếp nguồn/đích và cross-attention, hay chỉ một ngăn xếp nhân quả.</t>
+          <t>Mô hình nhận lời nhắc trong cùng một chuỗi và sinh token tiếp theo theo kiểu tự hồi quy mà không có encoder riêng hay cross-attention thuộc họ kiến trúc Transformer chỉ có decoder (Decoder-only Transformer, như GPT, LLaMA).</t>
         </is>
       </c>
     </row>
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G11" s="3" t="n"/>
       <c r="H11" s="4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>60</v>
@@ -1048,7 +1048,7 @@
       <c r="J11" s="3" t="n"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Dữ liệu không chỉ có một câu trả lời đích; nó so sánh hai câu trả lời.</t>
+          <t>Tập dữ liệu gồm chỉ dẫn, hai câu trả lời A/B và nhãn người đánh giá thích A hơn B là dữ liệu so sánh ưu tiên trực tiếp phục vụ giai đoạn căn chỉnh theo ưu tiên (preference alignment, như RLHF hoặc DPO).</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C, 4-D</t>
+          <t>1-B, 2-A, 3-C, 4-D</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1160,7 +1160,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Phân biệt dữ liệu giám sát, mô hình chấm điểm và mô hình sinh câu trả lời.</t>
+          <t>Câu trả lời mẫu do con người viết (x1) là đích giám sát cho hành vi ban đầu (SFT target) (r1); Nhãn ưu tiên A hơn B (x2) là tín hiệu xếp hạng các câu trả lời (r2); Mô hình thưởng (x3) ước lượng điểm thưởng cho câu trả lời (r3); Mô hình chính sách policy (x4) là mô hình sinh câu trả lời được tối ưu (r4).</t>
         </is>
       </c>
     </row>
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G15" s="3" t="n"/>
       <c r="H15" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4" t="n">
         <v>60</v>
@@ -1258,7 +1258,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tìm pipeline không có bước huấn luyện reward model riêng và vòng lặp tối ưu policy bằng RL.</t>
+          <t>Phương pháp tối ưu policy trực tiếp từ các cặp câu trả lời ưu tiên với một policy tham chiếu mà không cần huấn luyện reward model riêng hay chạy thuật toán RL là DPO (Direct Preference Optimization).</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>2,3</t>
+          <t>1,2</t>
         </is>
       </c>
       <c r="I16" s="4" t="n">
@@ -1315,7 +1315,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Đừng loại bỏ các cặp ưu tiên chỉ vì phương pháp này được gọi là trực tiếp.</t>
+          <t>DPO tối ưu trực tiếp policy từ dữ liệu ưu tiên thông qua hàm mất mát dạng phân loại nhị phân, do đó không cần giai đoạn huấn luyện reward model riêng (a) và không cần vòng lặp học tăng cường PPO (b).</t>
         </is>
       </c>
     </row>
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I17" s="4" t="n">
         <v>60</v>
@@ -1363,7 +1363,7 @@
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Giữ phạm vi đối tượng và nhiệm vụ trong kết luận trùng với phạm vi của bài đánh giá.</t>
+          <t>Đạt 99% trên một bài đánh giá an toàn cố định chỉ chứng minh mô hình có hiệu năng cao trên phân phối của bài đánh giá đó; trong thực tế triển khai, mô hình vẫn cần được kiểm thử trên các phân phối và kiểu tấn công đối kháng khác.</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1418,7 +1418,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Chọn bằng chứng quan sát hành vi trong nhiều điều kiện; đừng coi tên thuật toán là bảo chứng.</t>
+          <t>Đánh giá an toàn toàn diện cần: Red-team bằng lời nhắc đối kháng (a), Đánh giá trên phân phối thực tế (b), Theo dõi dạng lỗi và độ không chắc chắn (c), và Kiểm tra mức tuân thủ chính sách theo rubric (e). Chỉ biết tên phương pháp (d) không phải là bằng chứng kiểm chứng.</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>1-A, 2-B, 3-C</t>
+          <t>1-C, 2-B, 3-A</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1474,7 +1474,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Hỏi thay đổi xảy ra trước mô hình nền, sau mô hình nền hay trong lúc suy luận.</t>
+          <t>Tăng kho dữ liệu và năng lực tính toán cho việc dự đoán token kế tiếp (x1) thuộc Tiền huấn luyện pre-training (r1); Tinh chỉnh theo chỉ dẫn/ưu tiên sau khi có base model (x2) thuộc Hậu huấn luyện post-training (r2); Giữ nguyên trọng số, thực hiện thêm nhiều bước suy luận/tìm kiếm khi trả lời (x3) thuộc Tính toán tại thời điểm suy luận test-time compute (r3).</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1524,7 +1524,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính token đầu vào và đầu ra riêng theo đúng đơn giá, rồi mới cộng hai khoản.</t>
+          <t>Chi phí token đầu vào = 120.000 × (2 USD / 1.000.000) = 0,24 USD. Chi phí token đầu ra = 30.000 × (8 USD / 1.000.000) = 0,24 USD. Tổng chi phí là 0,24 + 0,24 = 0,48 USD.</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1574,7 +1574,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính tổng chi phí của từng nhà cung cấp bằng hai đơn giá riêng, rồi lấy chi phí của B trừ chi phí của A.</t>
+          <t>Chi phí tại Nhà cung cấp A = (800.000 × 0,50 + 200.000 × 1,50) / 1.000.000 = 0,40 + 0,30 = 0,70 USD. Chi phí tại Nhà cung cấp B = (800.000 × 0,70 + 200.000 × 1,00) / 1.000.000 = 0,56 + 0,20 = 0,76 USD. Chênh lệch chi phí: B − A = 0,76 − 0,70 = 0,06 USD (A rẻ hơn B 0,06 USD).</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -1625,7 +1625,7 @@
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Nhân số token của một request với 50 trước, rồi áp riêng hai đơn giá.</t>
+          <t>Tổng số token đầu vào cả lô = 50 × 4.000 = 200.000 token, chi phí đầu vào = 200.000 × (3 / 1.000.000) = 0,60 USD. Tổng số token đầu ra cả lô = 50 × 1.000 = 50.000 token, chi phí đầu ra = 50.000 × (9 / 1.000.000) = 0,45 USD. Tổng chi phí toàn bộ lô = 0,60 + 0,45 = 1,05 USD.</t>
         </is>
       </c>
     </row>
